--- a/luban-excels/xlsx/Items - 副本.xlsx
+++ b/luban-excels/xlsx/Items - 副本.xlsx
@@ -4260,7 +4260,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4271,9 +4271,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4934,11 +4931,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="19" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="18" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="19" customWidth="1"/>
+    <col min="23" max="23" width="7" style="18" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -5137,7 +5134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:35">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:35">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -5146,71 +5143,71 @@
       <c r="D3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="4" t="s">
+      <c r="S3" s="7"/>
+      <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="8"/>
-      <c r="X3" s="4" t="s">
+      <c r="W3" s="7"/>
+      <c r="X3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" s="4" t="s">
+      <c r="AH3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AI3" s="4" t="s">
+      <c r="AI3" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5315,72 +5312,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="18" customFormat="1" spans="1:35">
-      <c r="B5" s="18">
+    <row r="5" s="17" customFormat="1" spans="1:35">
+      <c r="B5" s="17">
         <v>1001</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <v>200</v>
       </c>
-      <c r="J5" s="18">
-        <v>0</v>
-      </c>
-      <c r="K5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="18" t="s">
+      <c r="J5" s="17">
+        <v>0</v>
+      </c>
+      <c r="K5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18">
-        <v>0</v>
-      </c>
-      <c r="P5" s="18">
-        <v>0</v>
-      </c>
-      <c r="T5" s="18" t="s">
+      <c r="M5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="17">
+        <v>0</v>
+      </c>
+      <c r="O5" s="17">
+        <v>0</v>
+      </c>
+      <c r="P5" s="17">
+        <v>0</v>
+      </c>
+      <c r="T5" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="U5" s="18" t="s">
+      <c r="U5" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="18">
+      <c r="V5" s="17">
         <v>1001</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="Y5" s="18" t="s">
+      <c r="W5" s="17"/>
+      <c r="Y5" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="18" t="b">
+      <c r="AA5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5844,10 +5841,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="12">
         <v>100</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="12">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -6562,7 +6559,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="19" t="s">
+      <c r="S23" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -6920,7 +6917,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="19" t="s">
+      <c r="S28" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -6932,7 +6929,7 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="19" t="s">
+      <c r="W28" s="18" t="s">
         <v>161</v>
       </c>
       <c r="X28">
@@ -7024,7 +7021,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="19" t="s">
+      <c r="S29" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -7036,7 +7033,7 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="19" t="s">
+      <c r="W29" s="18" t="s">
         <v>161</v>
       </c>
       <c r="X29">
@@ -7413,435 +7410,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="18" customFormat="1" spans="2:31">
-      <c r="B35" s="18">
+    <row r="35" s="17" customFormat="1" spans="2:31">
+      <c r="B35" s="17">
         <v>4001</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="18">
-        <v>0</v>
-      </c>
-      <c r="J35" s="18">
-        <v>0</v>
-      </c>
-      <c r="K35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" s="18" t="s">
+      <c r="I35" s="17">
+        <v>0</v>
+      </c>
+      <c r="J35" s="17">
+        <v>0</v>
+      </c>
+      <c r="K35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="18">
-        <v>0</v>
-      </c>
-      <c r="O35" s="18">
-        <v>0</v>
-      </c>
-      <c r="P35" s="18">
-        <v>0</v>
-      </c>
-      <c r="T35" s="18" t="s">
+      <c r="M35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17">
+        <v>0</v>
+      </c>
+      <c r="O35" s="17">
+        <v>0</v>
+      </c>
+      <c r="P35" s="17">
+        <v>0</v>
+      </c>
+      <c r="T35" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="U35" s="18" t="s">
+      <c r="U35" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="X35" s="18">
+      <c r="X35" s="17">
         <v>104001</v>
       </c>
-      <c r="Y35" s="18" t="s">
+      <c r="Y35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="18" customFormat="1" spans="2:31">
-      <c r="B36" s="18">
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="17" customFormat="1" spans="2:31">
+      <c r="B36" s="17">
         <v>4002</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H36" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="18">
-        <v>0</v>
-      </c>
-      <c r="J36" s="18">
-        <v>0</v>
-      </c>
-      <c r="K36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="18" t="s">
+      <c r="I36" s="17">
+        <v>0</v>
+      </c>
+      <c r="J36" s="17">
+        <v>0</v>
+      </c>
+      <c r="K36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="18">
-        <v>0</v>
-      </c>
-      <c r="O36" s="18">
-        <v>0</v>
-      </c>
-      <c r="P36" s="18">
-        <v>0</v>
-      </c>
-      <c r="T36" s="18" t="s">
+      <c r="M36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="17">
+        <v>0</v>
+      </c>
+      <c r="O36" s="17">
+        <v>0</v>
+      </c>
+      <c r="P36" s="17">
+        <v>0</v>
+      </c>
+      <c r="T36" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="U36" s="18" t="s">
+      <c r="U36" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="X36" s="18">
+      <c r="X36" s="17">
         <v>104002</v>
       </c>
-      <c r="Y36" s="18" t="s">
+      <c r="Y36" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="18" customFormat="1" spans="2:31">
-      <c r="B37" s="18">
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="17" customFormat="1" spans="2:31">
+      <c r="B37" s="17">
         <v>4003</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="18">
-        <v>0</v>
-      </c>
-      <c r="J37" s="18">
-        <v>0</v>
-      </c>
-      <c r="K37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" s="18" t="s">
+      <c r="I37" s="17">
+        <v>0</v>
+      </c>
+      <c r="J37" s="17">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="18">
-        <v>0</v>
-      </c>
-      <c r="O37" s="18">
-        <v>0</v>
-      </c>
-      <c r="P37" s="18">
-        <v>0</v>
-      </c>
-      <c r="T37" s="18" t="s">
+      <c r="M37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="17">
+        <v>0</v>
+      </c>
+      <c r="O37" s="17">
+        <v>0</v>
+      </c>
+      <c r="P37" s="17">
+        <v>0</v>
+      </c>
+      <c r="T37" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="U37" s="18" t="s">
+      <c r="U37" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="X37" s="18">
+      <c r="X37" s="17">
         <v>104003</v>
       </c>
-      <c r="Y37" s="18" t="s">
+      <c r="Y37" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="18" customFormat="1" spans="2:31">
-      <c r="B38" s="18">
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="17" customFormat="1" spans="2:31">
+      <c r="B38" s="17">
         <v>4004</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="18">
-        <v>0</v>
-      </c>
-      <c r="J38" s="18">
-        <v>0</v>
-      </c>
-      <c r="K38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" s="18" t="s">
+      <c r="I38" s="17">
+        <v>0</v>
+      </c>
+      <c r="J38" s="17">
+        <v>0</v>
+      </c>
+      <c r="K38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="18">
-        <v>0</v>
-      </c>
-      <c r="O38" s="18">
-        <v>0</v>
-      </c>
-      <c r="P38" s="18">
-        <v>0</v>
-      </c>
-      <c r="T38" s="18" t="s">
+      <c r="M38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="17">
+        <v>0</v>
+      </c>
+      <c r="O38" s="17">
+        <v>0</v>
+      </c>
+      <c r="P38" s="17">
+        <v>0</v>
+      </c>
+      <c r="T38" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="U38" s="18" t="s">
+      <c r="U38" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="X38" s="18">
+      <c r="X38" s="17">
         <v>104004</v>
       </c>
-      <c r="Y38" s="18" t="s">
+      <c r="Y38" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="18" customFormat="1" spans="2:31">
-      <c r="B39" s="18">
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="17" customFormat="1" spans="2:31">
+      <c r="B39" s="17">
         <v>4005</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I39" s="18">
-        <v>0</v>
-      </c>
-      <c r="J39" s="18">
-        <v>0</v>
-      </c>
-      <c r="K39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="18" t="s">
+      <c r="I39" s="17">
+        <v>0</v>
+      </c>
+      <c r="J39" s="17">
+        <v>0</v>
+      </c>
+      <c r="K39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="18">
-        <v>0</v>
-      </c>
-      <c r="O39" s="18">
-        <v>0</v>
-      </c>
-      <c r="P39" s="18">
-        <v>0</v>
-      </c>
-      <c r="T39" s="18" t="s">
+      <c r="M39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="17">
+        <v>0</v>
+      </c>
+      <c r="O39" s="17">
+        <v>0</v>
+      </c>
+      <c r="P39" s="17">
+        <v>0</v>
+      </c>
+      <c r="T39" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="U39" s="18" t="s">
+      <c r="U39" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="X39" s="18">
+      <c r="X39" s="17">
         <v>104005</v>
       </c>
-      <c r="Y39" s="18" t="s">
+      <c r="Y39" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="18" customFormat="1" spans="2:31">
-      <c r="B40" s="18">
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="17" customFormat="1" spans="2:31">
+      <c r="B40" s="17">
         <v>4006</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="H40" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="18">
-        <v>0</v>
-      </c>
-      <c r="J40" s="18">
-        <v>0</v>
-      </c>
-      <c r="K40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" s="18" t="s">
+      <c r="I40" s="17">
+        <v>0</v>
+      </c>
+      <c r="J40" s="17">
+        <v>0</v>
+      </c>
+      <c r="K40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40" s="18">
-        <v>0</v>
-      </c>
-      <c r="O40" s="18">
-        <v>0</v>
-      </c>
-      <c r="P40" s="18">
-        <v>0</v>
-      </c>
-      <c r="T40" s="18" t="s">
+      <c r="M40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="17">
+        <v>0</v>
+      </c>
+      <c r="O40" s="17">
+        <v>0</v>
+      </c>
+      <c r="P40" s="17">
+        <v>0</v>
+      </c>
+      <c r="T40" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="U40" s="18" t="s">
+      <c r="U40" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="X40" s="18">
+      <c r="X40" s="17">
         <v>104006</v>
       </c>
-      <c r="Y40" s="18" t="s">
+      <c r="Y40" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="18" t="b">
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8389,87 +8386,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="18" customFormat="1" spans="2:31">
-      <c r="B49" s="18">
+    <row r="49" s="17" customFormat="1" spans="2:31">
+      <c r="B49" s="17">
         <v>6001</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="18" t="s">
+      <c r="F49" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I49" s="18">
-        <v>300</v>
-      </c>
-      <c r="J49" s="18">
-        <v>0</v>
-      </c>
-      <c r="K49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="18" t="s">
+      <c r="I49" s="17">
+        <v>300</v>
+      </c>
+      <c r="J49" s="17">
+        <v>0</v>
+      </c>
+      <c r="K49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M49" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="18">
-        <v>0</v>
-      </c>
-      <c r="O49" s="18">
-        <v>0</v>
-      </c>
-      <c r="P49" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" s="18" t="s">
+      <c r="M49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="17">
+        <v>0</v>
+      </c>
+      <c r="O49" s="17">
+        <v>0</v>
+      </c>
+      <c r="P49" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="U49" s="18" t="s">
+      <c r="U49" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="X49" s="18">
+      <c r="X49" s="17">
         <v>106001</v>
       </c>
-      <c r="Y49" s="18" t="s">
+      <c r="Y49" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z49" s="18"/>
-      <c r="AA49" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="18" t="b">
+      <c r="Z49" s="17"/>
+      <c r="AA49" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8525,7 +8522,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="19" t="s">
+      <c r="S50" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -8608,7 +8605,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="19" t="s">
+      <c r="S51" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -8691,7 +8688,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="19" t="s">
+      <c r="S52" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -8774,7 +8771,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="19" t="s">
+      <c r="S53" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -8857,7 +8854,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="19" t="s">
+      <c r="S54" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -8940,7 +8937,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="19" t="s">
+      <c r="S55" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -9023,7 +9020,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="19" t="s">
+      <c r="S56" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -9106,7 +9103,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="19" t="s">
+      <c r="S57" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -9189,7 +9186,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="19" t="s">
+      <c r="S58" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -9272,7 +9269,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="19" t="s">
+      <c r="S59" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -9507,72 +9504,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="18" customFormat="1" spans="2:31">
-      <c r="B63" s="18">
+    <row r="63" s="17" customFormat="1" spans="2:31">
+      <c r="B63" s="17">
         <v>7004</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="21" t="s">
+      <c r="H63" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I63" s="18">
-        <v>300</v>
-      </c>
-      <c r="J63" s="18">
-        <v>0</v>
-      </c>
-      <c r="K63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="18" t="s">
+      <c r="I63" s="17">
+        <v>300</v>
+      </c>
+      <c r="J63" s="17">
+        <v>0</v>
+      </c>
+      <c r="K63" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63" s="18">
-        <v>0</v>
-      </c>
-      <c r="O63" s="18">
-        <v>0</v>
-      </c>
-      <c r="P63" s="18">
-        <v>0</v>
-      </c>
-      <c r="T63" s="18" t="s">
+      <c r="M63" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="17">
+        <v>0</v>
+      </c>
+      <c r="O63" s="17">
+        <v>0</v>
+      </c>
+      <c r="P63" s="17">
+        <v>0</v>
+      </c>
+      <c r="T63" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="U63" s="18" t="s">
+      <c r="U63" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="X63" s="18">
+      <c r="X63" s="17">
         <v>107004</v>
       </c>
-      <c r="Y63" s="18" t="s">
+      <c r="Y63" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z63" s="18"/>
-      <c r="AA63" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="18" t="b">
+      <c r="Z63" s="17"/>
+      <c r="AA63" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9589,7 +9586,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="12" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -9657,7 +9654,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="13" t="s">
+      <c r="H65" s="12" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -9832,7 +9829,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="19" t="s">
+      <c r="S67" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -9915,7 +9912,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="19" t="s">
+      <c r="S68" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -9998,7 +9995,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="19" t="s">
+      <c r="S69" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -10081,7 +10078,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="19" t="s">
+      <c r="S70" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -10164,7 +10161,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="19" t="s">
+      <c r="S71" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -10247,7 +10244,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="19" t="s">
+      <c r="S72" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -10330,7 +10327,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="19" t="s">
+      <c r="S73" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -10413,7 +10410,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="19" t="s">
+      <c r="S74" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -10496,7 +10493,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="19" t="s">
+      <c r="S75" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -10579,7 +10576,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="19" t="s">
+      <c r="S76" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -10733,7 +10730,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="19" t="s">
+      <c r="S78" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -10745,7 +10742,7 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="19" t="s">
+      <c r="W78" s="18" t="s">
         <v>161</v>
       </c>
       <c r="X78">
@@ -10834,7 +10831,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="19" t="s">
+      <c r="S79" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -10917,7 +10914,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="19" t="s">
+      <c r="S80" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -11000,7 +10997,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="19" t="s">
+      <c r="S81" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -11083,7 +11080,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="19" t="s">
+      <c r="S82" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -11166,7 +11163,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="19" t="s">
+      <c r="S83" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -11249,7 +11246,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="19" t="s">
+      <c r="S84" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -11539,7 +11536,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="19" t="s">
+      <c r="S88" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -11551,7 +11548,7 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="19" t="s">
+      <c r="W88" s="18" t="s">
         <v>161</v>
       </c>
       <c r="X88">
@@ -11643,7 +11640,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="19" t="s">
+      <c r="S89" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -11655,7 +11652,7 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="19" t="s">
+      <c r="W89" s="18" t="s">
         <v>161</v>
       </c>
       <c r="X89">
@@ -11818,7 +11815,7 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="19" t="s">
+      <c r="W91" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X91">
@@ -11898,7 +11895,7 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="19" t="s">
+      <c r="W92" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X92">
@@ -11978,7 +11975,7 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="19" t="s">
+      <c r="W93" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X93">
@@ -12058,7 +12055,7 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="19" t="s">
+      <c r="W94" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X94">
@@ -12138,7 +12135,7 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="19" t="s">
+      <c r="W95" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X95">
@@ -12218,7 +12215,7 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="19" t="s">
+      <c r="W96" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X96">
@@ -12298,7 +12295,7 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="19" t="s">
+      <c r="W97" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X97">
@@ -12372,7 +12369,7 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="19" t="s">
+      <c r="W98" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X98">
@@ -12529,7 +12526,7 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="19" t="s">
+      <c r="W100" s="18" t="s">
         <v>446</v>
       </c>
       <c r="X100">
@@ -12554,216 +12551,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" s="18" customFormat="1" spans="2:31">
-      <c r="B101" s="18">
+    <row r="101" s="17" customFormat="1" spans="2:31">
+      <c r="B101" s="17">
         <v>10001</v>
       </c>
-      <c r="C101" s="18" t="s">
+      <c r="C101" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D101" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E101" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="H101" s="18" t="s">
+      <c r="H101" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I101" s="18">
-        <v>300</v>
-      </c>
-      <c r="J101" s="18">
-        <v>0</v>
-      </c>
-      <c r="K101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" s="18" t="s">
+      <c r="I101" s="17">
+        <v>300</v>
+      </c>
+      <c r="J101" s="17">
+        <v>0</v>
+      </c>
+      <c r="K101" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101" s="18">
-        <v>0</v>
-      </c>
-      <c r="O101" s="18">
-        <v>0</v>
-      </c>
-      <c r="P101" s="18">
-        <v>0</v>
-      </c>
-      <c r="T101" s="18" t="s">
+      <c r="M101" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="17">
+        <v>0</v>
+      </c>
+      <c r="O101" s="17">
+        <v>0</v>
+      </c>
+      <c r="P101" s="17">
+        <v>0</v>
+      </c>
+      <c r="T101" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="U101" s="18" t="s">
+      <c r="U101" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="X101" s="18">
+      <c r="X101" s="17">
         <v>110001</v>
       </c>
-      <c r="Y101" s="18" t="s">
+      <c r="Y101" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z101" s="18"/>
-      <c r="AA101" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" s="18" customFormat="1" spans="2:31">
-      <c r="B102" s="18">
+      <c r="Z101" s="17"/>
+      <c r="AA101" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="17" customFormat="1" spans="2:31">
+      <c r="B102" s="17">
         <v>11001</v>
       </c>
-      <c r="C102" s="18" t="s">
+      <c r="C102" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="E102" s="18" t="s">
+      <c r="E102" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="H102" s="18" t="s">
+      <c r="H102" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I102" s="18">
-        <v>300</v>
-      </c>
-      <c r="J102" s="18">
-        <v>0</v>
-      </c>
-      <c r="K102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" s="18" t="s">
+      <c r="I102" s="17">
+        <v>300</v>
+      </c>
+      <c r="J102" s="17">
+        <v>0</v>
+      </c>
+      <c r="K102" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102" s="18">
-        <v>0</v>
-      </c>
-      <c r="O102" s="18">
-        <v>0</v>
-      </c>
-      <c r="P102" s="18">
-        <v>0</v>
-      </c>
-      <c r="T102" s="18" t="s">
+      <c r="M102" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="17">
+        <v>0</v>
+      </c>
+      <c r="O102" s="17">
+        <v>0</v>
+      </c>
+      <c r="P102" s="17">
+        <v>0</v>
+      </c>
+      <c r="T102" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="U102" s="18" t="s">
+      <c r="U102" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="18" t="s">
+      <c r="W102" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="X102" s="18">
+      <c r="X102" s="17">
         <v>111001</v>
       </c>
-      <c r="Y102" s="18" t="s">
+      <c r="Y102" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z102" s="18"/>
-      <c r="AA102" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" s="18" customFormat="1" spans="2:31">
-      <c r="B103" s="18">
+      <c r="Z102" s="17"/>
+      <c r="AA102" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="17" customFormat="1" spans="2:31">
+      <c r="B103" s="17">
         <v>11002</v>
       </c>
-      <c r="C103" s="18" t="s">
+      <c r="C103" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="D103" s="18" t="s">
+      <c r="D103" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E103" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="G103" s="18">
+      <c r="G103" s="17">
         <v>11001</v>
       </c>
-      <c r="H103" s="18" t="s">
+      <c r="H103" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I103" s="18">
-        <v>300</v>
-      </c>
-      <c r="J103" s="18">
-        <v>0</v>
-      </c>
-      <c r="K103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" s="18" t="s">
+      <c r="I103" s="17">
+        <v>300</v>
+      </c>
+      <c r="J103" s="17">
+        <v>0</v>
+      </c>
+      <c r="K103" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="M103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103" s="18">
-        <v>0</v>
-      </c>
-      <c r="O103" s="18">
-        <v>0</v>
-      </c>
-      <c r="P103" s="18">
-        <v>0</v>
-      </c>
-      <c r="T103" s="18" t="s">
+      <c r="M103" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="17">
+        <v>0</v>
+      </c>
+      <c r="O103" s="17">
+        <v>0</v>
+      </c>
+      <c r="P103" s="17">
+        <v>0</v>
+      </c>
+      <c r="T103" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="U103" s="18" t="s">
+      <c r="U103" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="X103" s="18">
+      <c r="X103" s="17">
         <v>111002</v>
       </c>
-      <c r="Y103" s="18" t="s">
+      <c r="Y103" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="Z103" s="18"/>
-      <c r="AA103" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="18" t="b">
+      <c r="Z103" s="17"/>
+      <c r="AA103" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12786,7 +12783,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="13" t="s">
+      <c r="H104" s="12" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -12819,7 +12816,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="19" t="s">
+      <c r="S104" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -12869,7 +12866,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="13" t="s">
+      <c r="H105" s="12" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -12902,7 +12899,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="19" t="s">
+      <c r="S105" s="18" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -12970,14 +12967,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="19"/>
+      <c r="S106" s="18"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="19" t="s">
+      <c r="W106" s="18" t="s">
         <v>509</v>
       </c>
       <c r="X106">
@@ -13040,7 +13037,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="19"/>
+      <c r="S107" s="18"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -13050,7 +13047,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="19" t="s">
+      <c r="W107" s="18" t="s">
         <v>509</v>
       </c>
       <c r="X107">
@@ -13260,62 +13257,62 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="77" customHeight="1" spans="1:19">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:19">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="1" t="s">
         <v>837</v>
       </c>
     </row>
@@ -13927,56 +13924,56 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="72" customHeight="1" spans="1:18">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:18">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="1" t="s">
         <v>904</v>
       </c>
     </row>
@@ -15561,7 +15558,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{9ab3edca-2e89-40f6-8d77-6a22e32bb9ff}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{2c3a927c-1d2d-45ac-b8e6-0c092d80231e}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -15639,16 +15636,16 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>161</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -15665,22 +15662,22 @@
       <c r="A4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>1041</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>598</v>
       </c>
     </row>
@@ -15697,13 +15694,13 @@
       <c r="D5">
         <v>199999</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -15720,10 +15717,10 @@
       <c r="D6">
         <v>299999</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>1046</v>
       </c>
       <c r="G6" t="s">
@@ -15743,13 +15740,13 @@
       <c r="D7">
         <v>229999</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>1048</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>1050</v>
       </c>
     </row>
@@ -15766,7 +15763,7 @@
       <c r="D8">
         <v>299999</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>1051</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -15904,7 +15901,7 @@
       <c r="D14">
         <v>409999</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>1069</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -15927,10 +15924,10 @@
       <c r="D15">
         <v>499999</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>1073</v>
       </c>
       <c r="G15" t="s">
@@ -15950,10 +15947,10 @@
       <c r="D16">
         <v>599999</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>1076</v>
       </c>
       <c r="G16" t="s">
@@ -15973,10 +15970,10 @@
       <c r="D17">
         <v>501999</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="1" t="s">
         <v>1079</v>
       </c>
       <c r="G17" t="s">
@@ -16019,10 +16016,10 @@
       <c r="D19">
         <v>599999</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="1" t="s">
         <v>1085</v>
       </c>
       <c r="G19" t="s">
@@ -16042,10 +16039,10 @@
       <c r="D20">
         <v>699999</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="G20" t="s">
@@ -16065,10 +16062,10 @@
       <c r="D21">
         <v>601999</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="1" t="s">
         <v>1091</v>
       </c>
       <c r="G21" t="s">
@@ -16088,10 +16085,10 @@
       <c r="D22">
         <v>602999</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="1" t="s">
         <v>1094</v>
       </c>
       <c r="G22" t="s">
@@ -16111,10 +16108,10 @@
       <c r="D23">
         <v>603999</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="G23" t="s">
@@ -16134,10 +16131,10 @@
       <c r="D24">
         <v>699999</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>1100</v>
       </c>
       <c r="G24" t="s">
@@ -16157,10 +16154,10 @@
       <c r="D25">
         <v>799999</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="1" t="s">
         <v>1103</v>
       </c>
       <c r="G25" t="s">
@@ -16203,10 +16200,10 @@
       <c r="D27">
         <v>700999</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>1108</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="1" t="s">
         <v>1109</v>
       </c>
       <c r="G27" t="s">
@@ -16226,10 +16223,10 @@
       <c r="D28">
         <v>701999</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>1111</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>1112</v>
       </c>
       <c r="G28" t="s">
@@ -16249,10 +16246,10 @@
       <c r="D29">
         <v>709999</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>1114</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="G29" t="s">
@@ -16295,10 +16292,10 @@
       <c r="D31">
         <v>999999</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>1121</v>
       </c>
       <c r="G31" t="s">
@@ -16318,63 +16315,54 @@
       <c r="D32">
         <v>99999</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>1123</v>
       </c>
       <c r="G32" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="33" spans="5:6">
-      <c r="E33" s="6"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="35" spans="5:6">
-      <c r="E35" s="6"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="5:6">
-      <c r="E36" s="6"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="5:6">
-      <c r="E37" s="6"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="5:6">
-      <c r="E38" s="6"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" spans="5:6">
-      <c r="E39" s="6"/>
-      <c r="F39" s="4"/>
-    </row>
-    <row r="40" spans="5:6">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="5:6">
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="5:6">
-      <c r="E43" s="6"/>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="5:6">
-      <c r="E44" s="6"/>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="5:6">
-      <c r="E45" s="6"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="47" spans="5:6">
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="5:6">
-      <c r="E48" s="6"/>
+    <row r="33" spans="5:5">
+      <c r="E33" s="5"/>
+    </row>
+    <row r="35" spans="5:5">
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="5:5">
+      <c r="E41" s="5"/>
+    </row>
+    <row r="43" spans="5:5">
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" s="5"/>
+    </row>
+    <row r="47" spans="5:5">
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="5:5">
+      <c r="E48" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16390,40 +16378,40 @@
   <cols>
     <col min="2" max="2" width="19.0833333333333" customWidth="1"/>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="8.66666666666667" style="5"/>
+    <col min="4" max="4" width="8.66666666666667" style="4"/>
     <col min="9" max="9" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>513</v>
       </c>
       <c r="E2" t="s">
@@ -16432,130 +16420,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="10">
-        <v>1</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="J2" s="9">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="9" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>2</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="9" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="9"/>
+      <c r="H4" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>4</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="9" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>8</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="9" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>540</v>
       </c>
       <c r="E6" t="s">
@@ -16564,521 +16552,521 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>16</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="9" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>32</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="9" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>64</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="9" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>128</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>256</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="9" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <v>512</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <v>1024</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="9" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <v>2048</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="9" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-    </row>
-    <row r="34" s="5" customFormat="1" spans="1:2">
-      <c r="A34" s="6" t="s">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+    </row>
+    <row r="34" s="4" customFormat="1" spans="1:2">
+      <c r="A34" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="35" s="5" customFormat="1" spans="1:2">
-      <c r="A35" s="6" t="s">
+    <row r="35" s="4" customFormat="1" spans="1:2">
+      <c r="A35" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="36" s="5" customFormat="1" spans="1:2">
-      <c r="A36" s="7" t="s">
+    <row r="36" s="4" customFormat="1" spans="1:2">
+      <c r="A36" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="37" s="5" customFormat="1" spans="1:2">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" s="5" customFormat="1" spans="1:2">
-      <c r="A38" s="6" t="s">
+    <row r="37" s="4" customFormat="1" spans="1:2">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" s="4" customFormat="1" spans="1:2">
+      <c r="A38" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="39" s="5" customFormat="1" spans="1:2">
-      <c r="A39" s="6" t="s">
+    <row r="39" s="4" customFormat="1" spans="1:2">
+      <c r="A39" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="40" s="5" customFormat="1" spans="1:2">
-      <c r="A40" s="6" t="s">
+    <row r="40" s="4" customFormat="1" spans="1:2">
+      <c r="A40" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="41" s="5" customFormat="1" spans="1:2">
-      <c r="A41" s="6" t="s">
+    <row r="41" s="4" customFormat="1" spans="1:2">
+      <c r="A41" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="42" s="5" customFormat="1" spans="1:2">
-      <c r="A42" s="7" t="s">
+    <row r="42" s="4" customFormat="1" spans="1:2">
+      <c r="A42" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="43" s="5" customFormat="1"/>
-    <row r="44" s="5" customFormat="1" spans="1:2">
-      <c r="A44" s="6" t="s">
+    <row r="43" s="4" customFormat="1"/>
+    <row r="44" s="4" customFormat="1" spans="1:2">
+      <c r="A44" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="1" spans="1:2">
-      <c r="A45" s="6" t="s">
+    <row r="45" s="4" customFormat="1" spans="1:2">
+      <c r="A45" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="46" s="5" customFormat="1" spans="1:2">
-      <c r="A46" s="7" t="s">
+    <row r="46" s="4" customFormat="1" spans="1:2">
+      <c r="A46" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="6"/>
-      <c r="B49" s="5"/>
+      <c r="A49" s="5"/>
+      <c r="B49" s="4"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="6"/>
-      <c r="B51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="A51" s="5"/>
+      <c r="B51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="G52" s="5"/>
+      <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="G53" s="5"/>
+      <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="G54" s="5"/>
+      <c r="G54" s="4"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="C58" s="5"/>
+      <c r="C58" s="4"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="4" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="4" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="4" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="4" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C66" s="5"/>
+      <c r="C66" s="4"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C67" s="5"/>
+      <c r="C67" s="4"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="C68" s="5"/>
+      <c r="C68" s="4"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>602</v>
       </c>
       <c r="B69" t="s">
@@ -17086,7 +17074,7 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>602</v>
       </c>
       <c r="B70" t="s">
@@ -17094,36 +17082,36 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="4" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="4" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C74" s="5"/>
+      <c r="C74" s="4"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>594</v>
       </c>
       <c r="B76" t="s">
@@ -17131,7 +17119,7 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>596</v>
       </c>
       <c r="B77" t="s">
@@ -17139,7 +17127,7 @@
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="7"/>
+      <c r="A78" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17257,88 +17245,88 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="109" customHeight="1" spans="1:14">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:14">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="1" spans="1:14">
+    <row r="4" s="4" customFormat="1" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>669</v>
       </c>
     </row>
@@ -17349,10 +17337,10 @@
       <c r="C5" t="s">
         <v>670</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>672</v>
       </c>
       <c r="F5">
@@ -17390,10 +17378,10 @@
       <c r="C6" t="s">
         <v>675</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>672</v>
       </c>
       <c r="F6">
@@ -17431,10 +17419,10 @@
       <c r="C7" t="s">
         <v>677</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>672</v>
       </c>
       <c r="F7">
@@ -17475,7 +17463,7 @@
       <c r="D8" t="s">
         <v>679</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>680</v>
       </c>
       <c r="F8">
@@ -17513,10 +17501,10 @@
       <c r="C9" t="s">
         <v>682</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>672</v>
       </c>
       <c r="F9">
@@ -17548,13 +17536,13 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="E16" s="10"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="10"/>
+      <c r="E17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17659,42 +17647,42 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="128" customHeight="1" spans="1:13">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>702</v>
       </c>
     </row>
@@ -18254,7 +18242,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="11" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="10" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18298,24 +18286,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="66" customHeight="1" spans="1:8">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="1" t="s">
         <v>667</v>
       </c>
     </row>
@@ -18355,7 +18343,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -18376,7 +18364,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -18397,7 +18385,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -18415,10 +18403,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>900</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -18436,10 +18424,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>180</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -18460,7 +18448,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -18472,7 +18460,7 @@
       <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -18490,7 +18478,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18511,7 +18499,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -18535,7 +18523,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -18556,7 +18544,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -18577,7 +18565,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -18598,7 +18586,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -18610,7 +18598,7 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -18778,7 +18766,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <f t="shared" ref="F28:F33" si="1">E28/10000</f>
         <v>0</v>
       </c>
@@ -18802,7 +18790,7 @@
       <c r="E29">
         <v>6700</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="10">
         <f t="shared" si="1"/>
         <v>0.67</v>
       </c>
@@ -18823,7 +18811,7 @@
       <c r="E30">
         <v>2200</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
@@ -18841,10 +18829,10 @@
       <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <v>900</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="10">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -18862,10 +18850,10 @@
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <v>180</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="10">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -18886,7 +18874,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="10">
         <f t="shared" si="1"/>
         <v>0.002</v>
       </c>
@@ -18895,7 +18883,7 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <f>SUM(F28:F33)</f>
         <v>1</v>
       </c>
@@ -18988,35 +18976,35 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>745</v>
       </c>
     </row>
@@ -20133,7 +20121,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -20141,20 +20129,20 @@
       <c r="C3" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>764</v>
       </c>
     </row>
@@ -20223,10 +20211,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -20246,10 +20234,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -20269,10 +20257,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -20292,10 +20280,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>140</v>
       </c>
       <c r="E9" t="s">
@@ -20315,10 +20303,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -20338,10 +20326,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>507</v>
       </c>
       <c r="E11" t="s">
@@ -20361,10 +20349,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>563</v>
       </c>
       <c r="E12" t="s">
@@ -20563,42 +20551,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="10"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
